--- a/artfynd/A 32001-2019 artfynd.xlsx
+++ b/artfynd/A 32001-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121171844</v>
       </c>
       <c r="B2" t="n">
-        <v>94562</v>
+        <v>94572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32001-2019 artfynd.xlsx
+++ b/artfynd/A 32001-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121171844</v>
       </c>
       <c r="B2" t="n">
-        <v>94572</v>
+        <v>94584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32001-2019 artfynd.xlsx
+++ b/artfynd/A 32001-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121171844</v>
       </c>
       <c r="B2" t="n">
-        <v>94584</v>
+        <v>94585</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32001-2019 artfynd.xlsx
+++ b/artfynd/A 32001-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121171844</v>
       </c>
       <c r="B2" t="n">
-        <v>94585</v>
+        <v>94588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32001-2019 artfynd.xlsx
+++ b/artfynd/A 32001-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121171844</v>
       </c>
       <c r="B2" t="n">
-        <v>94588</v>
+        <v>94594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
